--- a/src/salary-data/2026.09/2026.09-results.xlsx
+++ b/src/salary-data/2026.09/2026.09-results.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="L2" s="16" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="M2" s="15" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="L3" s="16" t="inlineStr">
         <is>
-          <t>27:59</t>
+          <t>2:16</t>
         </is>
       </c>
       <c r="M3" s="15" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="L4" s="16" t="inlineStr">
         <is>
-          <t>24:48</t>
+          <t>2:10</t>
         </is>
       </c>
       <c r="M4" s="15" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="L5" s="16" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>7:06</t>
         </is>
       </c>
       <c r="M5" s="15" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="L7" s="16" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>9:49</t>
         </is>
       </c>
       <c r="M7" s="15" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="L10" s="16" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>2:13</t>
         </is>
       </c>
       <c r="M10" s="15" t="n">
